--- a/data/seed/schedule.xlsx
+++ b/data/seed/schedule.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,16 @@
           <t>окончание</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>тип участка</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>фаза</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -584,12 +594,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12.4.4</t>
+          <t>12.3.10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Надземный каркас</t>
+          <t>Гидроизоляция, обратная засыпка</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,93 +609,125 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12.3.10</t>
+          <t>12.4.4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Гидроизоляция, обратная засыпка</t>
+          <t>Надземный каркас</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-02-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>12.5.1</t>
+          <t>12.4.10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Наружные сети</t>
+          <t>Бетонирование колонн и перекрытий</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BUILDING_FOOTPRINT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SUPERSTRUCTURE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12.4.8</t>
+          <t>12.5.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Стены, кровля, фасад</t>
+          <t>Наружные сети</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2026-12-25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>12.4.8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Стены, кровля, фасад</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>12.7</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Благоустройство</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2027-07-01</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2027-08-31</t>
         </is>
